--- a/work excel.xlsx
+++ b/work excel.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\OneDrive\Desktop\itbase in\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\itbasein_program\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="89">
   <si>
     <t xml:space="preserve">ITBASE.IN WORK </t>
   </si>
@@ -104,9 +104,6 @@
     <t>Sunday</t>
   </si>
   <si>
-    <t>done</t>
-  </si>
-  <si>
     <t>dictionary intoduction</t>
   </si>
   <si>
@@ -177,13 +174,133 @@
   </si>
   <si>
     <t>30/3/2026</t>
+  </si>
+  <si>
+    <t>Django project example</t>
+  </si>
+  <si>
+    <t>complete</t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>3 hr.</t>
+  </si>
+  <si>
+    <t>4 hr</t>
+  </si>
+  <si>
+    <t>13/5/2026</t>
+  </si>
+  <si>
+    <t>15/5/2026</t>
+  </si>
+  <si>
+    <t>18/5/2026</t>
+  </si>
+  <si>
+    <t>20/5/2026</t>
+  </si>
+  <si>
+    <t>22/5/2026</t>
+  </si>
+  <si>
+    <t>25/5/2026</t>
+  </si>
+  <si>
+    <t>27/5/2026</t>
+  </si>
+  <si>
+    <t>29/5/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/4/2026 to 4/5/2026 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crud Operations in Django </t>
+  </si>
+  <si>
+    <t xml:space="preserve">introduction Postgesql </t>
+  </si>
+  <si>
+    <t>Postgresql  tables</t>
+  </si>
+  <si>
+    <t>postgresql  tables insert /update query</t>
+  </si>
+  <si>
+    <t>collage Exam Leave</t>
+  </si>
+  <si>
+    <t>2  tables joining</t>
+  </si>
+  <si>
+    <t>create a sow for ai project(open code ai)</t>
+  </si>
+  <si>
+    <t>create a promp for ai script for project</t>
+  </si>
+  <si>
+    <t>starting yourcars opencode ai project</t>
+  </si>
+  <si>
+    <t>changes car imges and project update</t>
+  </si>
+  <si>
+    <t>add 3d view in yourcars project</t>
+  </si>
+  <si>
+    <t>dsa - Searching, sorting, bit manupulation, Hashing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dsa introduction </t>
+  </si>
+  <si>
+    <t>dsa- seraching algorithm -</t>
+  </si>
+  <si>
+    <t>dsa matrices,</t>
+  </si>
+  <si>
+    <t>dsa - tower of hanoi</t>
+  </si>
+  <si>
+    <t>live project upload</t>
+  </si>
+  <si>
+    <t>dsa script for videos</t>
+  </si>
+  <si>
+    <t>starting ai library</t>
+  </si>
+  <si>
+    <t>basic introduction of library</t>
+  </si>
+  <si>
+    <t>Numpy library</t>
+  </si>
+  <si>
+    <t>pandas library</t>
+  </si>
+  <si>
+    <t>matplotlib library</t>
+  </si>
+  <si>
+    <t>Numpy practical</t>
+  </si>
+  <si>
+    <t>scikit-learn library</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
+  </numFmts>
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -219,8 +336,80 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF006100"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF9C6500"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF9C0006"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial Rounded MT Bold"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -242,8 +431,13 @@
         <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -251,26 +445,90 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="2"/>
-    <xf numFmtId="14" fontId="3" fillId="3" borderId="0" xfId="2" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="11" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="5">
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
+    <cellStyle name="Calculation" xfId="4" builtinId="22"/>
     <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Neutral" xfId="3" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -551,495 +809,798 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K84"/>
+  <dimension ref="A1:K89"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.44140625" customWidth="1"/>
-    <col min="2" max="2" width="39.109375" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+    <col min="1" max="1" width="20.44140625" style="7" customWidth="1"/>
+    <col min="2" max="2" width="64.6640625" customWidth="1"/>
+    <col min="3" max="3" width="23.21875" style="7" customWidth="1"/>
     <col min="4" max="4" width="8.88671875" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+    </row>
+    <row r="2" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2"/>
+      <c r="C2"/>
+    </row>
+    <row r="3" spans="1:11" s="3" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.35">
+      <c r="A3" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B3" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C3" s="11" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="D3" s="9"/>
+    </row>
+    <row r="4" spans="1:11" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+      <c r="A4" s="8"/>
+      <c r="B4" s="20" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="C4" s="8"/>
+      <c r="D4" s="9"/>
+    </row>
+    <row r="5" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B5" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C5" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="9"/>
+    </row>
+    <row r="6" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A6" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="9"/>
+    </row>
+    <row r="7" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A7" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" s="9"/>
+    </row>
+    <row r="8" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A8" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="9"/>
+    </row>
+    <row r="9" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A9" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="9"/>
+    </row>
+    <row r="10" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A10" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" s="9"/>
+    </row>
+    <row r="11" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A11" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" s="9"/>
+    </row>
+    <row r="12" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" s="9"/>
+    </row>
+    <row r="13" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A13" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" s="9"/>
+      <c r="K13" s="1"/>
+    </row>
+    <row r="14" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A14" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" s="9"/>
+    </row>
+    <row r="15" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A15" s="8"/>
+      <c r="B15" s="19">
+        <v>46024</v>
+      </c>
+      <c r="C15" s="8"/>
+      <c r="D15" s="9"/>
+    </row>
+    <row r="16" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A16" s="10">
+        <v>46024</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="8"/>
+      <c r="D16" s="9"/>
+    </row>
+    <row r="17" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A17" s="10">
+        <v>46055</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" s="9"/>
+    </row>
+    <row r="18" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A18" s="10">
+        <v>46083</v>
+      </c>
+      <c r="B18" s="9" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" t="s">
-        <v>26</v>
-      </c>
-      <c r="K12" s="1"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B14" s="4">
-        <v>46024</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="2">
-        <v>46024</v>
-      </c>
-      <c r="B15" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="2">
-        <v>46055</v>
-      </c>
-      <c r="B16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="2">
-        <v>46083</v>
-      </c>
-      <c r="B17" t="s">
+      <c r="C18" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" s="9"/>
+    </row>
+    <row r="19" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A19" s="10">
+        <v>46114</v>
+      </c>
+      <c r="B19" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C17" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="2">
-        <v>46114</v>
-      </c>
-      <c r="B18" t="s">
+      <c r="C19" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D19" s="9"/>
+    </row>
+    <row r="20" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A20" s="10">
+        <v>46175</v>
+      </c>
+      <c r="B20" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C18" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="2">
-        <v>46175</v>
-      </c>
-      <c r="B19" t="s">
+      <c r="C20" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D20" s="9"/>
+    </row>
+    <row r="21" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A21" s="10">
+        <v>46267</v>
+      </c>
+      <c r="B21" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C19" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="2">
-        <v>46267</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="C21" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D21" s="9"/>
+    </row>
+    <row r="22" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A22" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C20" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
+      <c r="B22" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C22" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D22" s="9"/>
+    </row>
+    <row r="23" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A23" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="C21" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
+      <c r="B23" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C23" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" s="9"/>
+    </row>
+    <row r="24" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A24" s="10"/>
+      <c r="B24" s="19">
+        <v>46025</v>
+      </c>
+      <c r="C24" s="8"/>
+      <c r="D24" s="9"/>
+    </row>
+    <row r="25" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A25" s="10">
+        <v>46056</v>
+      </c>
+      <c r="B25" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C22" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="2">
-        <v>46056</v>
-      </c>
-      <c r="B23" t="s">
+      <c r="C25" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D25" s="9"/>
+    </row>
+    <row r="26" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A26" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C23" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
+      <c r="B26" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D26" s="9"/>
+    </row>
+    <row r="27" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A27" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B27" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C24" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" t="s">
+      <c r="C27" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D27" s="9"/>
+    </row>
+    <row r="28" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A28" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C25" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
+      <c r="B28" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D28" s="9"/>
+    </row>
+    <row r="29" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A29" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B29" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="C26" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B27" t="s">
+      <c r="C29" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D29" s="9"/>
+    </row>
+    <row r="30" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A30" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="C27" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
+      <c r="B30" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D30" s="9"/>
+    </row>
+    <row r="31" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A31" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B31" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D31" s="9"/>
+    </row>
+    <row r="32" spans="1:4" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+      <c r="A32" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C28" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B29" t="s">
-        <v>46</v>
-      </c>
-      <c r="C29" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
+      <c r="B32" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C32" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D32" s="9"/>
+    </row>
+    <row r="33" spans="1:4" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+      <c r="A33" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="C30" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
+      <c r="B33" s="9" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="2"/>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" s="2"/>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" s="2"/>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35" s="2"/>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36" s="2"/>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A37" s="2"/>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A38" s="2"/>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A39" s="2"/>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A40" s="2"/>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A41" s="2"/>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A42" s="2"/>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A43" s="2"/>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A44" s="2"/>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A45" s="2"/>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A46" s="2"/>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A47" s="2"/>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A48" s="2"/>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A49" s="2"/>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A50" s="2"/>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A51" s="2"/>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A52" s="2"/>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A53" s="2"/>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A54" s="2"/>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A55" s="2"/>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A56" s="2"/>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A57" s="2"/>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A58" s="2"/>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A59" s="2"/>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A60" s="2"/>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A61" s="2"/>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A62" s="2"/>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A63" s="2"/>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A64" s="2"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="9"/>
+    </row>
+    <row r="34" spans="1:4" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+      <c r="A34" s="10"/>
+      <c r="B34" s="19">
+        <v>46026</v>
+      </c>
+      <c r="C34" s="8"/>
+      <c r="D34" s="9"/>
+    </row>
+    <row r="35" spans="1:4" s="5" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A35" s="12">
+        <v>46026</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="C35" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D35" s="13" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" s="5" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A36" s="12">
+        <v>46085</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="C36" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D36" s="13" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" s="5" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A37" s="12">
+        <v>46177</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="C37" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D37" s="13" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" s="5" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A38" s="12">
+        <v>46269</v>
+      </c>
+      <c r="B38" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C38" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D38" s="13" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" s="23" customFormat="1" ht="36.6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="B39" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="C39" s="22"/>
+      <c r="D39" s="22"/>
+    </row>
+    <row r="40" spans="1:4" s="5" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A40" s="14"/>
+      <c r="B40" s="19">
+        <v>46027</v>
+      </c>
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+    </row>
+    <row r="41" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A41" s="12">
+        <v>46117</v>
+      </c>
+      <c r="B41" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C41" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D41" s="9"/>
+    </row>
+    <row r="42" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A42" s="12">
+        <v>46147</v>
+      </c>
+      <c r="B42" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C42" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D42" s="9"/>
+    </row>
+    <row r="43" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A43" s="12">
+        <v>46178</v>
+      </c>
+      <c r="B43" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C43" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D43" s="9"/>
+    </row>
+    <row r="44" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A44" s="12">
+        <v>46208</v>
+      </c>
+      <c r="B44" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C44" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D44" s="9"/>
+    </row>
+    <row r="45" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A45" s="12">
+        <v>46270</v>
+      </c>
+      <c r="B45" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C45" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D45" s="9"/>
+    </row>
+    <row r="46" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A46" s="12">
+        <v>46331</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="C46" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D46" s="9"/>
+    </row>
+    <row r="47" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A47" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B47" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C47" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D47" s="9"/>
+    </row>
+    <row r="48" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A48" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="B48" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C48" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D48" s="9"/>
+    </row>
+    <row r="49" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A49" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="B49" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="C49" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D49" s="9"/>
+    </row>
+    <row r="50" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A50" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C50" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D50" s="9"/>
+    </row>
+    <row r="51" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A51" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="C51" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D51" s="9"/>
+    </row>
+    <row r="52" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A52" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B52" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C52" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D52" s="9"/>
+    </row>
+    <row r="53" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A53" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B53" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D53" s="9"/>
+    </row>
+    <row r="54" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A54" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B54" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D54" s="9"/>
+    </row>
+    <row r="55" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A55" s="8"/>
+      <c r="B55" s="19">
+        <v>46028</v>
+      </c>
+      <c r="C55" s="8"/>
+      <c r="D55" s="9"/>
+    </row>
+    <row r="56" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A56" s="17">
+        <v>46028</v>
+      </c>
+      <c r="B56" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D56" s="9"/>
+    </row>
+    <row r="57" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A57" s="17">
+        <v>46087</v>
+      </c>
+      <c r="B57" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D57" s="9"/>
+    </row>
+    <row r="58" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A58" s="17">
+        <v>46148</v>
+      </c>
+      <c r="B58" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A59" s="17">
+        <v>46240</v>
+      </c>
+      <c r="B59" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="C59" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A60" s="17">
+        <v>46301</v>
+      </c>
+      <c r="B60" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A61" s="17">
+        <v>46362</v>
+      </c>
+      <c r="B61" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A62" s="17"/>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A63" s="6"/>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A64" s="6"/>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A65" s="2"/>
+      <c r="A65" s="6"/>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A66" s="2"/>
+      <c r="A66" s="6"/>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A67" s="2"/>
+      <c r="A67" s="6"/>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A68" s="2"/>
+      <c r="A68" s="6"/>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A69" s="2"/>
+      <c r="A69" s="6"/>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A70" s="2"/>
+      <c r="A70" s="6"/>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A71" s="2"/>
+      <c r="A71" s="6"/>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A72" s="2"/>
+      <c r="A72" s="6"/>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A73" s="2"/>
+      <c r="A73" s="6"/>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A74" s="2"/>
+      <c r="A74" s="6"/>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A75" s="2"/>
+      <c r="A75" s="6"/>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A76" s="2"/>
+      <c r="A76" s="6"/>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A77" s="2"/>
+      <c r="A77" s="6"/>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A78" s="2"/>
+      <c r="A78" s="6"/>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A79" s="2"/>
+      <c r="A79" s="6"/>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A80" s="2"/>
+      <c r="A80" s="6"/>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A81" s="2"/>
+      <c r="A81" s="6"/>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A82" s="2"/>
+      <c r="A82" s="6"/>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A83" s="2"/>
+      <c r="A83" s="6"/>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A84" s="2"/>
+      <c r="A84" s="6"/>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A85" s="6"/>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A86" s="6"/>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A87" s="6"/>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A88" s="6"/>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A89" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B39:D39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/work excel.xlsx
+++ b/work excel.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="88">
   <si>
     <t xml:space="preserve">ITBASE.IN WORK </t>
   </si>
@@ -180,9 +180,6 @@
   </si>
   <si>
     <t>complete</t>
-  </si>
-  <si>
-    <t>Completed</t>
   </si>
   <si>
     <t>3 hr.</t>
@@ -809,7 +806,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K89"/>
+  <dimension ref="A1:K95"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.44140625" style="7" customWidth="1"/>
@@ -842,32 +839,24 @@
       </c>
       <c r="D3" s="9"/>
     </row>
-    <row r="4" spans="1:11" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A4" s="8"/>
-      <c r="B4" s="20" t="s">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4"/>
+      <c r="C4"/>
+    </row>
+    <row r="5" spans="1:11" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+      <c r="A5" s="8"/>
+      <c r="B5" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="8"/>
-      <c r="D4" s="9"/>
-    </row>
-    <row r="5" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>51</v>
-      </c>
+      <c r="C5" s="8"/>
       <c r="D5" s="9"/>
     </row>
     <row r="6" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>51</v>
@@ -876,10 +865,10 @@
     </row>
     <row r="7" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>51</v>
@@ -888,19 +877,19 @@
     </row>
     <row r="8" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>23</v>
@@ -912,22 +901,22 @@
     </row>
     <row r="10" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="D10" s="9"/>
     </row>
     <row r="11" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>51</v>
@@ -936,10 +925,10 @@
     </row>
     <row r="12" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>51</v>
@@ -948,77 +937,71 @@
     </row>
     <row r="13" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>51</v>
       </c>
       <c r="D13" s="9"/>
-      <c r="K13" s="1"/>
     </row>
     <row r="14" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" s="9"/>
+      <c r="K14" s="1"/>
+    </row>
+    <row r="15" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A15" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B15" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D14" s="9"/>
-    </row>
-    <row r="15" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A15" s="8"/>
-      <c r="B15" s="19">
-        <v>46024</v>
-      </c>
-      <c r="C15" s="8"/>
+      <c r="C15" s="8" t="s">
+        <v>51</v>
+      </c>
       <c r="D15" s="9"/>
     </row>
     <row r="16" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A16" s="10">
-        <v>46024</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>25</v>
-      </c>
+      <c r="A16" s="8"/>
+      <c r="B16" s="9"/>
       <c r="C16" s="8"/>
       <c r="D16" s="9"/>
     </row>
     <row r="17" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A17" s="10">
-        <v>46055</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>51</v>
-      </c>
+      <c r="A17" s="8"/>
+      <c r="B17" s="19">
+        <v>46024</v>
+      </c>
+      <c r="C17" s="8"/>
       <c r="D17" s="9"/>
     </row>
     <row r="18" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A18" s="10">
-        <v>46083</v>
+        <v>46024</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>51</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="C18" s="8"/>
       <c r="D18" s="9"/>
     </row>
     <row r="19" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A19" s="10">
-        <v>46114</v>
+        <v>46055</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>51</v>
@@ -1027,10 +1010,10 @@
     </row>
     <row r="20" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A20" s="10">
-        <v>46175</v>
+        <v>46083</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C20" s="8" t="s">
         <v>51</v>
@@ -1039,90 +1022,84 @@
     </row>
     <row r="21" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A21" s="10">
+        <v>46114</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D21" s="9"/>
+    </row>
+    <row r="22" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A22" s="10">
+        <v>46175</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D22" s="9"/>
+    </row>
+    <row r="23" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A23" s="10">
         <v>46267</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B23" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C21" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D21" s="9"/>
-    </row>
-    <row r="22" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A22" s="10" t="s">
+      <c r="C23" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" s="9"/>
+    </row>
+    <row r="24" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A24" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B24" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C22" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D22" s="9"/>
-    </row>
-    <row r="23" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A23" s="10" t="s">
+      <c r="C24" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D24" s="9"/>
+    </row>
+    <row r="25" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A25" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B25" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C23" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D23" s="9"/>
-    </row>
-    <row r="24" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A24" s="10"/>
-      <c r="B24" s="19">
+      <c r="C25" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D25" s="9"/>
+    </row>
+    <row r="26" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A26" s="10"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="9"/>
+    </row>
+    <row r="27" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A27" s="10"/>
+      <c r="B27" s="19">
         <v>46025</v>
       </c>
-      <c r="C24" s="8"/>
-      <c r="D24" s="9"/>
-    </row>
-    <row r="25" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A25" s="10">
+      <c r="C27" s="8"/>
+      <c r="D27" s="9"/>
+    </row>
+    <row r="28" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A28" s="10">
         <v>46056</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B28" s="9" t="s">
         <v>34</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D25" s="9"/>
-    </row>
-    <row r="26" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A26" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="B26" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D26" s="9"/>
-    </row>
-    <row r="27" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A27" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="B27" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D27" s="9"/>
-    </row>
-    <row r="28" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A28" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="B28" s="9" t="s">
-        <v>41</v>
       </c>
       <c r="C28" s="8" t="s">
         <v>51</v>
@@ -1131,10 +1108,10 @@
     </row>
     <row r="29" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C29" s="8" t="s">
         <v>51</v>
@@ -1143,10 +1120,10 @@
     </row>
     <row r="30" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A30" s="10" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C30" s="8" t="s">
         <v>51</v>
@@ -1155,419 +1132,455 @@
     </row>
     <row r="31" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D31" s="9"/>
+    </row>
+    <row r="32" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A32" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D32" s="9"/>
+    </row>
+    <row r="33" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A33" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D33" s="9"/>
+    </row>
+    <row r="34" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A34" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="B34" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="C31" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D31" s="9"/>
-    </row>
-    <row r="32" spans="1:4" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A32" s="10" t="s">
+      <c r="C34" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D34" s="9"/>
+    </row>
+    <row r="35" spans="1:4" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+      <c r="A35" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B32" s="9" t="s">
+      <c r="B35" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C32" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D32" s="9"/>
-    </row>
-    <row r="33" spans="1:4" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A33" s="10" t="s">
+      <c r="C35" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D35" s="9"/>
+    </row>
+    <row r="36" spans="1:4" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+      <c r="A36" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="B36" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C33" s="8"/>
-      <c r="D33" s="9"/>
-    </row>
-    <row r="34" spans="1:4" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A34" s="10"/>
-      <c r="B34" s="19">
+      <c r="C36" s="8"/>
+      <c r="D36" s="9"/>
+    </row>
+    <row r="37" spans="1:4" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+      <c r="A37" s="10"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="9"/>
+    </row>
+    <row r="38" spans="1:4" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+      <c r="A38" s="10"/>
+      <c r="B38" s="19">
         <v>46026</v>
       </c>
-      <c r="C34" s="8"/>
-      <c r="D34" s="9"/>
-    </row>
-    <row r="35" spans="1:4" s="5" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A35" s="12">
+      <c r="C38" s="8"/>
+      <c r="D38" s="9"/>
+    </row>
+    <row r="39" spans="1:4" s="5" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A39" s="12">
         <v>46026</v>
       </c>
-      <c r="B35" s="13" t="s">
+      <c r="B39" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="C39" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D39" s="13" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" s="5" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A40" s="12">
+        <v>46085</v>
+      </c>
+      <c r="B40" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="C35" s="14" t="s">
+      <c r="C40" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D40" s="13" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" s="5" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A41" s="12">
+        <v>46177</v>
+      </c>
+      <c r="B41" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="C41" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D41" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="D35" s="13" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" s="5" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A36" s="12">
-        <v>46085</v>
-      </c>
-      <c r="B36" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="C36" s="14" t="s">
+    </row>
+    <row r="42" spans="1:4" s="5" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A42" s="12">
+        <v>46269</v>
+      </c>
+      <c r="B42" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="C42" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D42" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="D36" s="13" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" s="5" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A37" s="12">
-        <v>46177</v>
-      </c>
-      <c r="B37" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="C37" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="D37" s="13" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" s="5" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A38" s="12">
-        <v>46269</v>
-      </c>
-      <c r="B38" s="13" t="s">
+    </row>
+    <row r="43" spans="1:4" s="23" customFormat="1" ht="36.6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="B43" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="C38" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="D38" s="13" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" s="23" customFormat="1" ht="36.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="B39" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="C39" s="22"/>
-      <c r="D39" s="22"/>
-    </row>
-    <row r="40" spans="1:4" s="5" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A40" s="14"/>
-      <c r="B40" s="19">
+      <c r="C43" s="22"/>
+      <c r="D43" s="22"/>
+    </row>
+    <row r="44" spans="1:4" s="23" customFormat="1" ht="36.6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="21"/>
+      <c r="B44" s="21"/>
+      <c r="C44" s="21"/>
+      <c r="D44" s="21"/>
+    </row>
+    <row r="45" spans="1:4" s="5" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A45" s="14"/>
+      <c r="B45" s="19">
         <v>46027</v>
       </c>
-      <c r="C40" s="18"/>
-      <c r="D40" s="18"/>
-    </row>
-    <row r="41" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A41" s="12">
-        <v>46117</v>
-      </c>
-      <c r="B41" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="C41" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="D41" s="9"/>
-    </row>
-    <row r="42" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A42" s="12">
-        <v>46147</v>
-      </c>
-      <c r="B42" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C42" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="D42" s="9"/>
-    </row>
-    <row r="43" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A43" s="12">
-        <v>46178</v>
-      </c>
-      <c r="B43" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="C43" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="D43" s="9"/>
-    </row>
-    <row r="44" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A44" s="12">
-        <v>46208</v>
-      </c>
-      <c r="B44" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="C44" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="D44" s="9"/>
-    </row>
-    <row r="45" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A45" s="12">
-        <v>46270</v>
-      </c>
-      <c r="B45" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="C45" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="D45" s="9"/>
+      <c r="C45" s="18"/>
+      <c r="D45" s="18"/>
     </row>
     <row r="46" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A46" s="12">
+        <v>46117</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C46" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D46" s="9"/>
+    </row>
+    <row r="47" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A47" s="12">
+        <v>46147</v>
+      </c>
+      <c r="B47" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C47" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D47" s="9"/>
+    </row>
+    <row r="48" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A48" s="12">
+        <v>46178</v>
+      </c>
+      <c r="B48" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C48" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D48" s="9"/>
+    </row>
+    <row r="49" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A49" s="12">
+        <v>46208</v>
+      </c>
+      <c r="B49" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C49" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D49" s="9"/>
+    </row>
+    <row r="50" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A50" s="12">
+        <v>46270</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C50" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D50" s="9"/>
+    </row>
+    <row r="51" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A51" s="12">
         <v>46331</v>
       </c>
-      <c r="B46" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="C46" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="D46" s="9"/>
-    </row>
-    <row r="47" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A47" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="B47" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="C47" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="D47" s="9"/>
-    </row>
-    <row r="48" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A48" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="B48" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="C48" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="D48" s="9"/>
-    </row>
-    <row r="49" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A49" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="B49" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="C49" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="D49" s="9"/>
-    </row>
-    <row r="50" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A50" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="B50" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="C50" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="D50" s="9"/>
-    </row>
-    <row r="51" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A51" s="14" t="s">
-        <v>59</v>
-      </c>
       <c r="B51" s="13" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D51" s="9"/>
     </row>
     <row r="52" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A52" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B52" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="C52" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D52" s="9"/>
+    </row>
+    <row r="53" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A53" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B53" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="C53" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D53" s="9"/>
+    </row>
+    <row r="54" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A54" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="B54" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="C54" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D54" s="9"/>
+    </row>
+    <row r="55" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A55" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="B55" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C55" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D55" s="9"/>
+    </row>
+    <row r="56" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A56" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="B56" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C56" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D56" s="9"/>
+    </row>
+    <row r="57" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A57" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="B57" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="C57" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D57" s="9"/>
+    </row>
+    <row r="58" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A58" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="B52" s="13" t="s">
+      <c r="B58" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="C52" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="D52" s="9"/>
-    </row>
-    <row r="53" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A53" s="8" t="s">
+      <c r="C58" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D58" s="9"/>
+    </row>
+    <row r="59" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A59" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="B53" s="16" t="s">
+      <c r="B59" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="C53" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="D53" s="9"/>
-    </row>
-    <row r="54" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A54" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="B54" s="16" t="s">
+      <c r="C59" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D59" s="9"/>
+    </row>
+    <row r="60" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A60" s="8"/>
+      <c r="B60" s="16"/>
+      <c r="C60" s="8"/>
+      <c r="D60" s="9"/>
+    </row>
+    <row r="61" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A61" s="8"/>
+      <c r="B61" s="19">
+        <v>46028</v>
+      </c>
+      <c r="C61" s="8"/>
+      <c r="D61" s="9"/>
+    </row>
+    <row r="62" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A62" s="17">
+        <v>46028</v>
+      </c>
+      <c r="B62" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="C54" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="D54" s="9"/>
-    </row>
-    <row r="55" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A55" s="8"/>
-      <c r="B55" s="19">
-        <v>46028</v>
-      </c>
-      <c r="C55" s="8"/>
-      <c r="D55" s="9"/>
-    </row>
-    <row r="56" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A56" s="17">
-        <v>46028</v>
-      </c>
-      <c r="B56" s="16" t="s">
+      <c r="C62" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D62" s="9"/>
+    </row>
+    <row r="63" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A63" s="17">
+        <v>46087</v>
+      </c>
+      <c r="B63" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="C56" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="D56" s="9"/>
-    </row>
-    <row r="57" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A57" s="17">
-        <v>46087</v>
-      </c>
-      <c r="B57" s="18" t="s">
+      <c r="C63" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D63" s="9"/>
+    </row>
+    <row r="64" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A64" s="17">
+        <v>46148</v>
+      </c>
+      <c r="B64" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A65" s="17">
+        <v>46240</v>
+      </c>
+      <c r="B65" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="C57" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="D57" s="9"/>
-    </row>
-    <row r="58" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A58" s="17">
-        <v>46148</v>
-      </c>
-      <c r="B58" s="18" t="s">
+      <c r="C65" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A66" s="17">
+        <v>46301</v>
+      </c>
+      <c r="B66" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A67" s="17">
+        <v>46362</v>
+      </c>
+      <c r="B67" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="C58" s="8" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A59" s="17">
-        <v>46240</v>
-      </c>
-      <c r="B59" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="C59" s="8" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A60" s="17">
-        <v>46301</v>
-      </c>
-      <c r="B60" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="C60" s="8" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A61" s="17">
-        <v>46362</v>
-      </c>
-      <c r="B61" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="C61" s="8" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A62" s="17"/>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A63" s="6"/>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A64" s="6"/>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A65" s="6"/>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A66" s="6"/>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A67" s="6"/>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A68" s="6"/>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C67" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A68" s="17"/>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" s="6"/>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" s="6"/>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" s="6"/>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" s="6"/>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" s="6"/>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" s="6"/>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" s="6"/>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" s="6"/>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" s="6"/>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" s="6"/>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" s="6"/>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" s="6"/>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.3">
@@ -1596,11 +1609,29 @@
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A89" s="6"/>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A90" s="6"/>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A91" s="6"/>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A92" s="6"/>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A93" s="6"/>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A94" s="6"/>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A95" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="B43:D43"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/work excel.xlsx
+++ b/work excel.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="90">
   <si>
     <t xml:space="preserve">ITBASE.IN WORK </t>
   </si>
@@ -288,6 +288,12 @@
   </si>
   <si>
     <t>scikit-learn library</t>
+  </si>
+  <si>
+    <t>15/6/2026</t>
+  </si>
+  <si>
+    <t>tensorflow library</t>
   </si>
 </sst>
 </file>
@@ -468,9 +474,6 @@
   <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -518,10 +521,13 @@
     <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
@@ -809,824 +815,829 @@
   <dimension ref="A1:K95"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.44140625" style="7" customWidth="1"/>
+    <col min="1" max="1" width="20.44140625" style="6" customWidth="1"/>
     <col min="2" max="2" width="64.6640625" customWidth="1"/>
-    <col min="3" max="3" width="23.21875" style="7" customWidth="1"/>
+    <col min="3" max="3" width="23.21875" style="6" customWidth="1"/>
     <col min="4" max="4" width="8.88671875" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
     </row>
     <row r="2" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2"/>
       <c r="C2"/>
     </row>
-    <row r="3" spans="1:11" s="3" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A3" s="11" t="s">
+    <row r="3" spans="1:11" s="2" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.35">
+      <c r="A3" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="9"/>
+      <c r="D3" s="8"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4"/>
       <c r="C4"/>
     </row>
-    <row r="5" spans="1:11" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A5" s="8"/>
-      <c r="B5" s="20" t="s">
+    <row r="5" spans="1:11" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+      <c r="A5" s="7"/>
+      <c r="B5" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="9"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="8"/>
     </row>
     <row r="6" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="9"/>
+      <c r="C6" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="8"/>
     </row>
     <row r="7" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D7" s="9"/>
+      <c r="C7" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" s="8"/>
     </row>
     <row r="8" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D8" s="9"/>
+      <c r="C8" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" s="8"/>
     </row>
     <row r="9" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="9"/>
+      <c r="D9" s="8"/>
     </row>
     <row r="10" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="9"/>
+      <c r="D10" s="8"/>
     </row>
     <row r="11" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D11" s="9"/>
+      <c r="C11" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" s="8"/>
     </row>
     <row r="12" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D12" s="9"/>
+      <c r="C12" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" s="8"/>
     </row>
     <row r="13" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D13" s="9"/>
+      <c r="C13" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" s="8"/>
     </row>
     <row r="14" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D14" s="9"/>
+      <c r="C14" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" s="8"/>
       <c r="K14" s="1"/>
     </row>
     <row r="15" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D15" s="9"/>
+      <c r="C15" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D15" s="8"/>
     </row>
     <row r="16" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A16" s="8"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="9"/>
+      <c r="A16" s="7"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="8"/>
     </row>
     <row r="17" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A17" s="8"/>
-      <c r="B17" s="19">
+      <c r="A17" s="7"/>
+      <c r="B17" s="18">
         <v>46024</v>
       </c>
-      <c r="C17" s="8"/>
-      <c r="D17" s="9"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="8"/>
     </row>
     <row r="18" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A18" s="10">
+      <c r="A18" s="9">
         <v>46024</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="8"/>
-      <c r="D18" s="9"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="8"/>
     </row>
     <row r="19" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A19" s="10">
+      <c r="A19" s="9">
         <v>46055</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D19" s="9"/>
+      <c r="C19" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D19" s="8"/>
     </row>
     <row r="20" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A20" s="10">
+      <c r="A20" s="9">
         <v>46083</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D20" s="9"/>
+      <c r="C20" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D20" s="8"/>
     </row>
     <row r="21" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A21" s="10">
+      <c r="A21" s="9">
         <v>46114</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D21" s="9"/>
+      <c r="C21" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D21" s="8"/>
     </row>
     <row r="22" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A22" s="10">
+      <c r="A22" s="9">
         <v>46175</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C22" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D22" s="9"/>
+      <c r="C22" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D22" s="8"/>
     </row>
     <row r="23" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A23" s="10">
+      <c r="A23" s="9">
         <v>46267</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C23" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D23" s="9"/>
+      <c r="C23" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" s="8"/>
     </row>
     <row r="24" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A24" s="10" t="s">
+      <c r="A24" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D24" s="9"/>
+      <c r="C24" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D24" s="8"/>
     </row>
     <row r="25" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A25" s="10" t="s">
+      <c r="A25" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B25" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C25" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D25" s="9"/>
+      <c r="C25" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D25" s="8"/>
     </row>
     <row r="26" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A26" s="10"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="9"/>
+      <c r="A26" s="9"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="8"/>
     </row>
     <row r="27" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A27" s="10"/>
-      <c r="B27" s="19">
+      <c r="A27" s="9"/>
+      <c r="B27" s="18">
         <v>46025</v>
       </c>
-      <c r="C27" s="8"/>
-      <c r="D27" s="9"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="8"/>
     </row>
     <row r="28" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A28" s="10">
+      <c r="A28" s="9">
         <v>46056</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C28" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D28" s="9"/>
+      <c r="C28" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D28" s="8"/>
     </row>
     <row r="29" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A29" s="10" t="s">
+      <c r="A29" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C29" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D29" s="9"/>
+      <c r="C29" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D29" s="8"/>
     </row>
     <row r="30" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A30" s="10" t="s">
+      <c r="A30" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B30" s="9" t="s">
+      <c r="B30" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C30" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D30" s="9"/>
+      <c r="C30" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D30" s="8"/>
     </row>
     <row r="31" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A31" s="10" t="s">
+      <c r="A31" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="B31" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C31" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D31" s="9"/>
+      <c r="C31" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D31" s="8"/>
     </row>
     <row r="32" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A32" s="10" t="s">
+      <c r="A32" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C32" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D32" s="9"/>
+      <c r="C32" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D32" s="8"/>
     </row>
     <row r="33" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A33" s="10" t="s">
+      <c r="A33" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="B33" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C33" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D33" s="9"/>
+      <c r="C33" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D33" s="8"/>
     </row>
     <row r="34" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A34" s="10" t="s">
+      <c r="A34" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="B34" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C34" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D34" s="9"/>
-    </row>
-    <row r="35" spans="1:4" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A35" s="10" t="s">
+      <c r="C34" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D34" s="8"/>
+    </row>
+    <row r="35" spans="1:4" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+      <c r="A35" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="B35" s="9" t="s">
+      <c r="B35" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="C35" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D35" s="9"/>
-    </row>
-    <row r="36" spans="1:4" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A36" s="10" t="s">
+      <c r="C35" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D35" s="8"/>
+    </row>
+    <row r="36" spans="1:4" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+      <c r="A36" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="B36" s="9" t="s">
+      <c r="B36" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C36" s="8"/>
-      <c r="D36" s="9"/>
-    </row>
-    <row r="37" spans="1:4" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A37" s="10"/>
-      <c r="B37" s="9"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="9"/>
-    </row>
-    <row r="38" spans="1:4" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A38" s="10"/>
-      <c r="B38" s="19">
+      <c r="C36" s="7"/>
+      <c r="D36" s="8"/>
+    </row>
+    <row r="37" spans="1:4" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+      <c r="A37" s="9"/>
+      <c r="B37" s="8"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="8"/>
+    </row>
+    <row r="38" spans="1:4" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+      <c r="A38" s="9"/>
+      <c r="B38" s="18">
         <v>46026</v>
       </c>
-      <c r="C38" s="8"/>
-      <c r="D38" s="9"/>
-    </row>
-    <row r="39" spans="1:4" s="5" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A39" s="12">
+      <c r="C38" s="7"/>
+      <c r="D38" s="8"/>
+    </row>
+    <row r="39" spans="1:4" s="4" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A39" s="11">
         <v>46026</v>
       </c>
-      <c r="B39" s="13" t="s">
+      <c r="B39" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="C39" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D39" s="13" t="s">
+      <c r="C39" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D39" s="12" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="40" spans="1:4" s="5" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A40" s="12">
+    <row r="40" spans="1:4" s="4" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A40" s="11">
         <v>46085</v>
       </c>
-      <c r="B40" s="13" t="s">
+      <c r="B40" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="C40" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D40" s="13" t="s">
+      <c r="C40" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D40" s="12" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="41" spans="1:4" s="5" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A41" s="12">
+    <row r="41" spans="1:4" s="4" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A41" s="11">
         <v>46177</v>
       </c>
-      <c r="B41" s="13" t="s">
+      <c r="B41" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="C41" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D41" s="13" t="s">
+      <c r="C41" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D41" s="12" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="42" spans="1:4" s="5" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A42" s="12">
+    <row r="42" spans="1:4" s="4" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A42" s="11">
         <v>46269</v>
       </c>
-      <c r="B42" s="13" t="s">
+      <c r="B42" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="C42" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D42" s="13" t="s">
+      <c r="C42" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D42" s="12" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="43" spans="1:4" s="23" customFormat="1" ht="36.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="21" t="s">
+    <row r="43" spans="1:4" s="21" customFormat="1" ht="36.6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="B43" s="22" t="s">
+      <c r="B43" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="C43" s="22"/>
-      <c r="D43" s="22"/>
-    </row>
-    <row r="44" spans="1:4" s="23" customFormat="1" ht="36.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="21"/>
-      <c r="B44" s="21"/>
-      <c r="C44" s="21"/>
-      <c r="D44" s="21"/>
-    </row>
-    <row r="45" spans="1:4" s="5" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A45" s="14"/>
-      <c r="B45" s="19">
+      <c r="C43" s="23"/>
+      <c r="D43" s="23"/>
+    </row>
+    <row r="44" spans="1:4" s="21" customFormat="1" ht="36.6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="20"/>
+      <c r="B44" s="20"/>
+      <c r="C44" s="20"/>
+      <c r="D44" s="20"/>
+    </row>
+    <row r="45" spans="1:4" s="4" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A45" s="13"/>
+      <c r="B45" s="18">
         <v>46027</v>
       </c>
-      <c r="C45" s="18"/>
-      <c r="D45" s="18"/>
+      <c r="C45" s="17"/>
+      <c r="D45" s="17"/>
     </row>
     <row r="46" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A46" s="12">
+      <c r="A46" s="11">
         <v>46117</v>
       </c>
-      <c r="B46" s="13" t="s">
+      <c r="B46" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="C46" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D46" s="9"/>
+      <c r="C46" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D46" s="8"/>
     </row>
     <row r="47" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A47" s="12">
+      <c r="A47" s="11">
         <v>46147</v>
       </c>
-      <c r="B47" s="13" t="s">
+      <c r="B47" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C47" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D47" s="9"/>
+      <c r="C47" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D47" s="8"/>
     </row>
     <row r="48" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A48" s="12">
+      <c r="A48" s="11">
         <v>46178</v>
       </c>
-      <c r="B48" s="13" t="s">
+      <c r="B48" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="C48" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D48" s="9"/>
+      <c r="C48" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D48" s="8"/>
     </row>
     <row r="49" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A49" s="12">
+      <c r="A49" s="11">
         <v>46208</v>
       </c>
-      <c r="B49" s="13" t="s">
+      <c r="B49" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C49" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D49" s="9"/>
+      <c r="C49" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D49" s="8"/>
     </row>
     <row r="50" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A50" s="12">
+      <c r="A50" s="11">
         <v>46270</v>
       </c>
-      <c r="B50" s="13" t="s">
+      <c r="B50" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C50" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D50" s="9"/>
+      <c r="C50" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D50" s="8"/>
     </row>
     <row r="51" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A51" s="12">
+      <c r="A51" s="11">
         <v>46331</v>
       </c>
-      <c r="B51" s="13" t="s">
+      <c r="B51" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="C51" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D51" s="9"/>
+      <c r="C51" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D51" s="8"/>
     </row>
     <row r="52" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A52" s="14" t="s">
+      <c r="A52" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="B52" s="13" t="s">
+      <c r="B52" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="C52" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D52" s="9"/>
+      <c r="C52" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D52" s="8"/>
     </row>
     <row r="53" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A53" s="14" t="s">
+      <c r="A53" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="B53" s="15" t="s">
+      <c r="B53" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="C53" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D53" s="9"/>
+      <c r="C53" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D53" s="8"/>
     </row>
     <row r="54" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A54" s="14" t="s">
+      <c r="A54" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="B54" s="15" t="s">
+      <c r="B54" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="C54" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D54" s="9"/>
+      <c r="C54" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D54" s="8"/>
     </row>
     <row r="55" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A55" s="14" t="s">
+      <c r="A55" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="B55" s="13" t="s">
+      <c r="B55" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="C55" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D55" s="9"/>
+      <c r="C55" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D55" s="8"/>
     </row>
     <row r="56" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A56" s="14" t="s">
+      <c r="A56" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="B56" s="13" t="s">
+      <c r="B56" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="C56" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D56" s="9"/>
+      <c r="C56" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D56" s="8"/>
     </row>
     <row r="57" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A57" s="14" t="s">
+      <c r="A57" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="B57" s="13" t="s">
+      <c r="B57" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="C57" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D57" s="9"/>
+      <c r="C57" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D57" s="8"/>
     </row>
     <row r="58" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A58" s="8" t="s">
+      <c r="A58" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B58" s="16" t="s">
+      <c r="B58" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="C58" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D58" s="9"/>
+      <c r="C58" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D58" s="8"/>
     </row>
     <row r="59" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A59" s="8" t="s">
+      <c r="A59" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="B59" s="16" t="s">
+      <c r="B59" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="C59" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D59" s="9"/>
+      <c r="C59" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D59" s="8"/>
     </row>
     <row r="60" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A60" s="8"/>
-      <c r="B60" s="16"/>
-      <c r="C60" s="8"/>
-      <c r="D60" s="9"/>
+      <c r="A60" s="7"/>
+      <c r="B60" s="15"/>
+      <c r="C60" s="7"/>
+      <c r="D60" s="8"/>
     </row>
     <row r="61" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A61" s="8"/>
-      <c r="B61" s="19">
+      <c r="A61" s="7"/>
+      <c r="B61" s="18">
         <v>46028</v>
       </c>
-      <c r="C61" s="8"/>
-      <c r="D61" s="9"/>
+      <c r="C61" s="7"/>
+      <c r="D61" s="8"/>
     </row>
     <row r="62" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A62" s="17">
+      <c r="A62" s="16">
         <v>46028</v>
       </c>
-      <c r="B62" s="16" t="s">
+      <c r="B62" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="C62" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D62" s="9"/>
+      <c r="C62" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D62" s="8"/>
     </row>
     <row r="63" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A63" s="17">
+      <c r="A63" s="16">
         <v>46087</v>
       </c>
-      <c r="B63" s="18" t="s">
+      <c r="B63" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="C63" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D63" s="9"/>
+      <c r="C63" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D63" s="8"/>
     </row>
     <row r="64" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A64" s="17">
+      <c r="A64" s="16">
         <v>46148</v>
       </c>
-      <c r="B64" s="18" t="s">
+      <c r="B64" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="C64" s="8" t="s">
+      <c r="C64" s="7" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A65" s="17">
+      <c r="A65" s="16">
         <v>46240</v>
       </c>
-      <c r="B65" s="16" t="s">
+      <c r="B65" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="C65" s="8" t="s">
+      <c r="C65" s="7" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A66" s="17">
+      <c r="A66" s="16">
         <v>46301</v>
       </c>
-      <c r="B66" s="9" t="s">
+      <c r="B66" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="C66" s="8" t="s">
+      <c r="C66" s="7" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A67" s="17">
+      <c r="A67" s="16">
         <v>46362</v>
       </c>
-      <c r="B67" s="9" t="s">
+      <c r="B67" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="C67" s="8" t="s">
+      <c r="C67" s="7" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A68" s="17"/>
+      <c r="A68" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="B68" s="8" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A69" s="6"/>
+      <c r="A69" s="5"/>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A70" s="6"/>
+      <c r="A70" s="5"/>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A71" s="6"/>
+      <c r="A71" s="5"/>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A72" s="6"/>
+      <c r="A72" s="5"/>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A73" s="6"/>
+      <c r="A73" s="5"/>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A74" s="6"/>
+      <c r="A74" s="5"/>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A75" s="6"/>
+      <c r="A75" s="5"/>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A76" s="6"/>
+      <c r="A76" s="5"/>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A77" s="6"/>
+      <c r="A77" s="5"/>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A78" s="6"/>
+      <c r="A78" s="5"/>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A79" s="6"/>
+      <c r="A79" s="5"/>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A80" s="6"/>
+      <c r="A80" s="5"/>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A81" s="6"/>
+      <c r="A81" s="5"/>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A82" s="6"/>
+      <c r="A82" s="5"/>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A83" s="6"/>
+      <c r="A83" s="5"/>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A84" s="6"/>
+      <c r="A84" s="5"/>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A85" s="6"/>
+      <c r="A85" s="5"/>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A86" s="6"/>
+      <c r="A86" s="5"/>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A87" s="6"/>
+      <c r="A87" s="5"/>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A88" s="6"/>
+      <c r="A88" s="5"/>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A89" s="6"/>
+      <c r="A89" s="5"/>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A90" s="6"/>
+      <c r="A90" s="5"/>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A91" s="6"/>
+      <c r="A91" s="5"/>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A92" s="6"/>
+      <c r="A92" s="5"/>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A93" s="6"/>
+      <c r="A93" s="5"/>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A94" s="6"/>
+      <c r="A94" s="5"/>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A95" s="6"/>
+      <c r="A95" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/work excel.xlsx
+++ b/work excel.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="92">
   <si>
     <t xml:space="preserve">ITBASE.IN WORK </t>
   </si>
@@ -294,6 +294,12 @@
   </si>
   <si>
     <t>tensorflow library</t>
+  </si>
+  <si>
+    <t>17/6/2027</t>
+  </si>
+  <si>
+    <t>keras library practical</t>
   </si>
 </sst>
 </file>
@@ -1276,7 +1282,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="43" spans="1:4" s="21" customFormat="1" ht="36.6" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4" s="21" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="20" t="s">
         <v>62</v>
       </c>
@@ -1286,11 +1292,9 @@
       <c r="C43" s="23"/>
       <c r="D43" s="23"/>
     </row>
-    <row r="44" spans="1:4" s="21" customFormat="1" ht="36.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="20"/>
-      <c r="B44" s="20"/>
-      <c r="C44" s="20"/>
-      <c r="D44" s="20"/>
+    <row r="44" spans="1:4" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44"/>
+      <c r="C44"/>
     </row>
     <row r="45" spans="1:4" s="4" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A45" s="13"/>
@@ -1557,9 +1561,20 @@
       <c r="B68" s="8" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A69" s="5"/>
+      <c r="C68" s="7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A69" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="B69" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" s="5"/>
